--- a/output/timetable_by_faculty.xlsx
+++ b/output/timetable_by_faculty.xlsx
@@ -594,7 +594,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>assignment:79:session:1</t>
+          <t>assignment:29:session:1</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -613,27 +613,27 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>AI Research Laboratory</t>
+          <t>Web Technologies Laboratory</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>MSC-AI</t>
+          <t>BSC-AI</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>M.Sc Artificial Intelligence</t>
+          <t>B.Sc Artificial Intelligence</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>MSC-AI-Y2-G1-B1</t>
+          <t>BSC-AI-Y2-G1-B1</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>M.Sc Artificial Intelligence Year 2 Group 1 Batch 1</t>
+          <t>B.Sc Artificial Intelligence Year 2 Group 1 Batch 1</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -643,53 +643,53 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>LAB302</t>
+          <t>LAB304</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>assignment:4:session:1</t>
+          <t>assignment:79:session:1</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>MONDAY</t>
+          <t>TUESDAY</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Programming Fundamentals Laboratory</t>
+          <t>AI Research Laboratory</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI</t>
+          <t>MSC-AI</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence</t>
+          <t>M.Sc Artificial Intelligence</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI-Y1-G1-B1</t>
+          <t>MSC-AI-Y2-G1-B1</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence Year 1 Group 1 Batch 1</t>
+          <t>M.Sc Artificial Intelligence Year 2 Group 1 Batch 1</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -699,53 +699,53 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>LAB302</t>
+          <t>LAB303</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>assignment:29:session:1</t>
+          <t>assignment:4:session:1</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>THURSDAY</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Web Technologies Laboratory</t>
+          <t>Programming Fundamentals Laboratory</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>BSC-AI</t>
+          <t>BTECH-AI</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>B.Sc Artificial Intelligence</t>
+          <t>B.Tech Artificial Intelligence</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>BSC-AI-Y2-G1-B1</t>
+          <t>BTECH-AI-Y1-G1-B1</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>B.Sc Artificial Intelligence Year 2 Group 1 Batch 1</t>
+          <t>B.Tech Artificial Intelligence Year 1 Group 1 Batch 1</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>LAB302</t>
+          <t>LAB303</t>
         </is>
       </c>
     </row>
@@ -767,14 +767,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>FRIDAY</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>2</v>
@@ -811,7 +811,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>LAB302</t>
+          <t>LAB304</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>assignment:71:session:2</t>
+          <t>assignment:11:session:3</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -929,27 +929,27 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Machine Learning</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>MSC-AI</t>
+          <t>BTECH-AI</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>M.Sc Artificial Intelligence</t>
+          <t>B.Tech Artificial Intelligence</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>MSC-AI-Y1-G1</t>
+          <t>BTECH-AI-Y3-G1</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>M.Sc Artificial Intelligence Year 1 Group 1</t>
+          <t>B.Tech Artificial Intelligence Year 3 Group 1</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>CR201</t>
+          <t>CR204</t>
         </is>
       </c>
     </row>
@@ -971,14 +971,14 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>WEDNESDAY</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1</v>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>CR208</t>
+          <t>CR201</t>
         </is>
       </c>
     </row>
@@ -1027,14 +1027,14 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>WEDNESDAY</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>CR202</t>
+          <t>CR205</t>
         </is>
       </c>
     </row>
@@ -1083,14 +1083,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>WEDNESDAY</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>1</v>
@@ -1127,53 +1127,53 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>CR201</t>
+          <t>CR204</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>assignment:11:session:2</t>
+          <t>assignment:71:session:3</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>WEDNESDAY</t>
+          <t>THURSDAY</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI</t>
+          <t>MSC-AI</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence</t>
+          <t>M.Sc Artificial Intelligence</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI-Y3-G1</t>
+          <t>MSC-AI-Y1-G1</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence Year 3 Group 1</t>
+          <t>M.Sc Artificial Intelligence Year 1 Group 1</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1183,26 +1183,26 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>CR201</t>
+          <t>CR203</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>assignment:41:session:3</t>
+          <t>assignment:41:session:1</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>WEDNESDAY</t>
+          <t>THURSDAY</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>1</v>
@@ -1246,7 +1246,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>assignment:71:session:3</t>
+          <t>assignment:11:session:2</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1255,37 +1255,37 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Machine Learning</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>MSC-AI</t>
+          <t>BTECH-AI</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>M.Sc Artificial Intelligence</t>
+          <t>B.Tech Artificial Intelligence</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>MSC-AI-Y1-G1</t>
+          <t>BTECH-AI-Y3-G1</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>M.Sc Artificial Intelligence Year 1 Group 1</t>
+          <t>B.Tech Artificial Intelligence Year 3 Group 1</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1295,53 +1295,53 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>CR201</t>
+          <t>CR204</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>assignment:11:session:3</t>
+          <t>assignment:41:session:3</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>FRIDAY</t>
+          <t>THURSDAY</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning</t>
+          <t>Data Management and AI Integration</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI</t>
+          <t>BCA-AI</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI-Y3-G1</t>
+          <t>BCA-AI-Y2-G1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence Year 3 Group 1</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence Year 2 Group 1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1358,7 +1358,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>assignment:41:session:1</t>
+          <t>assignment:71:session:2</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1367,37 +1367,37 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Data Management and AI Integration</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI</t>
+          <t>MSC-AI</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
+          <t>M.Sc Artificial Intelligence</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI-Y2-G1</t>
+          <t>MSC-AI-Y1-G1</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence Year 2 Group 1</t>
+          <t>M.Sc Artificial Intelligence Year 1 Group 1</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>CR207</t>
+          <t>CR202</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>assignment:18:session:3</t>
+          <t>assignment:78:session:3</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -1515,37 +1515,37 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Agentic AI</t>
+          <t>Computer Vision</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI</t>
+          <t>MSC-AI</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence</t>
+          <t>M.Sc Artificial Intelligence</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI-Y4-G1</t>
+          <t>MSC-AI-Y2-G1</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence Year 4 Group 1</t>
+          <t>M.Sc Artificial Intelligence Year 2 Group 1</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -1562,7 +1562,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>assignment:78:session:3</t>
+          <t>assignment:48:session:2</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -1571,37 +1571,37 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Computer Vision</t>
+          <t>Machine Learning</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>MSC-AI</t>
+          <t>BCA-AI</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>M.Sc Artificial Intelligence</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>MSC-AI-Y2-G1</t>
+          <t>BCA-AI-Y3-G1</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>M.Sc Artificial Intelligence Year 2 Group 1</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence Year 3 Group 1</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>assignment:78:session:1</t>
+          <t>assignment:18:session:1</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -1627,37 +1627,37 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Computer Vision</t>
+          <t>Agentic AI</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>MSC-AI</t>
+          <t>BTECH-AI</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>M.Sc Artificial Intelligence</t>
+          <t>B.Tech Artificial Intelligence</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>MSC-AI-Y2-G1</t>
+          <t>BTECH-AI-Y4-G1</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>M.Sc Artificial Intelligence Year 2 Group 1</t>
+          <t>B.Tech Artificial Intelligence Year 4 Group 1</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1674,7 +1674,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>assignment:78:session:2</t>
+          <t>assignment:48:session:1</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -1683,37 +1683,37 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Computer Vision</t>
+          <t>Machine Learning</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>MSC-AI</t>
+          <t>BCA-AI</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>M.Sc Artificial Intelligence</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>MSC-AI-Y2-G1</t>
+          <t>BCA-AI-Y3-G1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>M.Sc Artificial Intelligence Year 2 Group 1</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence Year 3 Group 1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1730,46 +1730,46 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>assignment:18:session:2</t>
+          <t>assignment:48:session:3</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>WEDNESDAY</t>
+          <t>TUESDAY</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Agentic AI</t>
+          <t>Machine Learning</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI</t>
+          <t>BCA-AI</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI-Y4-G1</t>
+          <t>BCA-AI-Y3-G1</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence Year 4 Group 1</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence Year 3 Group 1</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>assignment:48:session:2</t>
+          <t>assignment:78:session:2</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -1795,37 +1795,37 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning</t>
+          <t>Computer Vision</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI</t>
+          <t>MSC-AI</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
+          <t>M.Sc Artificial Intelligence</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI-Y3-G1</t>
+          <t>MSC-AI-Y2-G1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence Year 3 Group 1</t>
+          <t>M.Sc Artificial Intelligence Year 2 Group 1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1842,7 +1842,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>assignment:18:session:1</t>
+          <t>assignment:18:session:3</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
@@ -1898,7 +1898,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>assignment:48:session:1</t>
+          <t>assignment:78:session:1</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1907,37 +1907,37 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning</t>
+          <t>Computer Vision</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI</t>
+          <t>MSC-AI</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
+          <t>M.Sc Artificial Intelligence</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI-Y3-G1</t>
+          <t>MSC-AI-Y2-G1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence Year 3 Group 1</t>
+          <t>M.Sc Artificial Intelligence Year 2 Group 1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>assignment:48:session:3</t>
+          <t>assignment:18:session:2</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1963,37 +1963,37 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning</t>
+          <t>Agentic AI</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI</t>
+          <t>BTECH-AI</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
+          <t>B.Tech Artificial Intelligence</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI-Y3-G1</t>
+          <t>BTECH-AI-Y4-G1</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence Year 3 Group 1</t>
+          <t>B.Tech Artificial Intelligence Year 4 Group 1</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>assignment:51:session:2</t>
+          <t>assignment:51:session:1</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -2151,14 +2151,14 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>CR206</t>
+          <t>CR202</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>assignment:51:session:1</t>
+          <t>assignment:21:session:2</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -2167,37 +2167,37 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Signal Theory</t>
+          <t>Mathematics for Computing</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>MTECH-AI</t>
+          <t>BSC-AI</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>M.Tech Artificial Intelligence</t>
+          <t>B.Sc Artificial Intelligence</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>MTECH-AI-Y1-G1</t>
+          <t>BSC-AI-Y1-G1</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>M.Tech Artificial Intelligence Year 1 Group 1</t>
+          <t>B.Sc Artificial Intelligence Year 1 Group 1</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -2219,14 +2219,14 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>WEDNESDAY</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1</v>
@@ -2270,46 +2270,46 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>assignment:21:session:1</t>
+          <t>assignment:51:session:3</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>WEDNESDAY</t>
+          <t>FRIDAY</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Mathematics for Computing</t>
+          <t>Signal Theory</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>BSC-AI</t>
+          <t>MTECH-AI</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>B.Sc Artificial Intelligence</t>
+          <t>M.Tech Artificial Intelligence</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>BSC-AI-Y1-G1</t>
+          <t>MTECH-AI-Y1-G1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>B.Sc Artificial Intelligence Year 1 Group 1</t>
+          <t>M.Tech Artificial Intelligence Year 1 Group 1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2319,14 +2319,14 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>CR202</t>
+          <t>CR208</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>assignment:21:session:2</t>
+          <t>assignment:21:session:1</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
@@ -2375,14 +2375,14 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>CR207</t>
+          <t>CR204</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>assignment:51:session:3</t>
+          <t>assignment:51:session:2</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>CR202</t>
+          <t>CR205</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>assignment:33:session:2</t>
+          <t>assignment:63:session:1</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -2539,37 +2539,37 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Data Science and Analytics</t>
+          <t>Mathematics for Computing</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>BSC-AI</t>
+          <t>MCA-AI</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>B.Sc Artificial Intelligence</t>
+          <t>MCA Artificial Intelligence</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>BSC-AI-Y3-G1</t>
+          <t>MCA-AI-Y1-G1</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>B.Sc Artificial Intelligence Year 3 Group 1</t>
+          <t>MCA Artificial Intelligence Year 1 Group 1</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -2579,19 +2579,19 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>ONLINE</t>
+          <t>CR205</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>assignment:63:session:2</t>
+          <t>assignment:63:session:3</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>MONDAY</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -2635,14 +2635,14 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>CR205</t>
+          <t>CR203</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>assignment:3:session:1</t>
+          <t>assignment:33:session:1</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -2651,37 +2651,37 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Digital Electronics</t>
+          <t>Data Science and Analytics</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI</t>
+          <t>BSC-AI</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence</t>
+          <t>B.Sc Artificial Intelligence</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI-Y1-G1</t>
+          <t>BSC-AI-Y3-G1</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence Year 1 Group 1</t>
+          <t>B.Sc Artificial Intelligence Year 3 Group 1</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2691,53 +2691,53 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>CR202</t>
+          <t>ONLINE</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>assignment:63:session:1</t>
+          <t>assignment:33:session:2</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>WEDNESDAY</t>
+          <t>TUESDAY</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Mathematics for Computing</t>
+          <t>Data Science and Analytics</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>MCA-AI</t>
+          <t>BSC-AI</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>MCA Artificial Intelligence</t>
+          <t>B.Sc Artificial Intelligence</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>MCA-AI-Y1-G1</t>
+          <t>BSC-AI-Y3-G1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>MCA Artificial Intelligence Year 1 Group 1</t>
+          <t>B.Sc Artificial Intelligence Year 3 Group 1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2747,53 +2747,53 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>CR202</t>
+          <t>ONLINE</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>assignment:33:session:1</t>
+          <t>assignment:3:session:1</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>WEDNESDAY</t>
+          <t>TUESDAY</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Data Science and Analytics</t>
+          <t>Digital Electronics</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>BSC-AI</t>
+          <t>BTECH-AI</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>B.Sc Artificial Intelligence</t>
+          <t>B.Tech Artificial Intelligence</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>BSC-AI-Y3-G1</t>
+          <t>BTECH-AI-Y1-G1</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>B.Sc Artificial Intelligence Year 3 Group 1</t>
+          <t>B.Tech Artificial Intelligence Year 1 Group 1</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>ONLINE</t>
+          <t>CR201</t>
         </is>
       </c>
     </row>
@@ -2815,14 +2815,14 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>THURSDAY</t>
+          <t>WEDNESDAY</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>1</v>
@@ -2866,7 +2866,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>assignment:3:session:2</t>
+          <t>assignment:63:session:2</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -2875,37 +2875,37 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Digital Electronics</t>
+          <t>Mathematics for Computing</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI</t>
+          <t>MCA-AI</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence</t>
+          <t>MCA Artificial Intelligence</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI-Y1-G1</t>
+          <t>MCA-AI-Y1-G1</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence Year 1 Group 1</t>
+          <t>MCA Artificial Intelligence Year 1 Group 1</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2915,26 +2915,26 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>CR201</t>
+          <t>CR206</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>assignment:3:session:3</t>
+          <t>assignment:3:session:2</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>FRIDAY</t>
+          <t>THURSDAY</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1</v>
@@ -2971,14 +2971,14 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>CR201</t>
+          <t>CR203</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>assignment:63:session:3</t>
+          <t>assignment:3:session:3</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -2987,37 +2987,37 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Mathematics for Computing</t>
+          <t>Digital Electronics</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>MCA-AI</t>
+          <t>BTECH-AI</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>MCA Artificial Intelligence</t>
+          <t>B.Tech Artificial Intelligence</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>MCA-AI-Y1-G1</t>
+          <t>BTECH-AI-Y1-G1</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>MCA Artificial Intelligence Year 1 Group 1</t>
+          <t>B.Tech Artificial Intelligence Year 1 Group 1</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>CR201</t>
+          <t>CR203</t>
         </is>
       </c>
     </row>
@@ -3126,19 +3126,19 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>assignment:62:session:1</t>
+          <t>assignment:62:session:2</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>MONDAY</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1</v>
@@ -3175,53 +3175,53 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>LH101</t>
+          <t>LH104</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>assignment:32:session:3</t>
+          <t>assignment:2:session:3</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>MONDAY</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning</t>
+          <t>Programming Fundamentals</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>BSC-AI</t>
+          <t>BTECH-AI</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>B.Sc Artificial Intelligence</t>
+          <t>B.Tech Artificial Intelligence</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>BSC-AI-Y3-G1</t>
+          <t>BTECH-AI-Y1-G1</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>B.Sc Artificial Intelligence Year 3 Group 1</t>
+          <t>B.Tech Artificial Intelligence Year 1 Group 1</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -3238,7 +3238,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>assignment:62:session:3</t>
+          <t>assignment:2:session:2</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -3247,37 +3247,37 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Data Science and Analytics</t>
+          <t>Programming Fundamentals</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>MCA-AI</t>
+          <t>BTECH-AI</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>MCA Artificial Intelligence</t>
+          <t>B.Tech Artificial Intelligence</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>MCA-AI-Y1-G1</t>
+          <t>BTECH-AI-Y1-G1</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>MCA Artificial Intelligence Year 1 Group 1</t>
+          <t>B.Tech Artificial Intelligence Year 1 Group 1</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -3287,14 +3287,14 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>LH101</t>
+          <t>CR202</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>assignment:32:session:1</t>
+          <t>assignment:32:session:3</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -3303,10 +3303,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>1</v>
@@ -3343,53 +3343,53 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>CR202</t>
+          <t>CR207</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>assignment:2:session:1</t>
+          <t>assignment:32:session:2</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>WEDNESDAY</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Programming Fundamentals</t>
+          <t>Machine Learning</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI</t>
+          <t>BSC-AI</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence</t>
+          <t>B.Sc Artificial Intelligence</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI-Y1-G1</t>
+          <t>BSC-AI-Y3-G1</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence Year 1 Group 1</t>
+          <t>B.Sc Artificial Intelligence Year 3 Group 1</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -3399,19 +3399,19 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>CR201</t>
+          <t>CR204</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>assignment:2:session:2</t>
+          <t>assignment:62:session:3</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>THURSDAY</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -3425,27 +3425,27 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Programming Fundamentals</t>
+          <t>Data Science and Analytics</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI</t>
+          <t>MCA-AI</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence</t>
+          <t>MCA Artificial Intelligence</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI-Y1-G1</t>
+          <t>MCA-AI-Y1-G1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence Year 1 Group 1</t>
+          <t>MCA Artificial Intelligence Year 1 Group 1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -3455,26 +3455,26 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>CR203</t>
+          <t>LH102</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>assignment:2:session:3</t>
+          <t>assignment:2:session:1</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>WEDNESDAY</t>
+          <t>FRIDAY</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
@@ -3511,26 +3511,26 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>CR201</t>
+          <t>CR203</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>assignment:32:session:2</t>
+          <t>assignment:32:session:1</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>THURSDAY</t>
+          <t>FRIDAY</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1</v>
@@ -3567,14 +3567,14 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>CR201</t>
+          <t>CR206</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>assignment:62:session:2</t>
+          <t>assignment:62:session:1</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -3583,10 +3583,10 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>1</v>
@@ -3722,19 +3722,19 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>assignment:23:session:3</t>
+          <t>assignment:23:session:2</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>MONDAY</t>
+          <t>TUESDAY</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1</v>
@@ -3771,53 +3771,53 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>CR203</t>
+          <t>CR207</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>assignment:23:session:1</t>
+          <t>assignment:53:session:2</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>THURSDAY</t>
+          <t>WEDNESDAY</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Computer Fundamentals</t>
+          <t>Mathematics for Computing</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>BSC-AI</t>
+          <t>MTECH-AI</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>B.Sc Artificial Intelligence</t>
+          <t>M.Tech Artificial Intelligence</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>BSC-AI-Y1-G1</t>
+          <t>MTECH-AI-Y1-G1</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>B.Sc Artificial Intelligence Year 1 Group 1</t>
+          <t>M.Tech Artificial Intelligence Year 1 Group 1</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -3827,53 +3827,53 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>CR201</t>
+          <t>ONLINE</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>assignment:23:session:2</t>
+          <t>assignment:53:session:1</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>THURSDAY</t>
+          <t>WEDNESDAY</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Computer Fundamentals</t>
+          <t>Mathematics for Computing</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>BSC-AI</t>
+          <t>MTECH-AI</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>B.Sc Artificial Intelligence</t>
+          <t>M.Tech Artificial Intelligence</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>BSC-AI-Y1-G1</t>
+          <t>MTECH-AI-Y1-G1</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>B.Sc Artificial Intelligence Year 1 Group 1</t>
+          <t>M.Tech Artificial Intelligence Year 1 Group 1</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -3883,53 +3883,53 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>CR204</t>
+          <t>ONLINE</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>assignment:53:session:2</t>
+          <t>assignment:23:session:1</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>FRIDAY</t>
+          <t>THURSDAY</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Mathematics for Computing</t>
+          <t>Computer Fundamentals</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>MTECH-AI</t>
+          <t>BSC-AI</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>M.Tech Artificial Intelligence</t>
+          <t>B.Sc Artificial Intelligence</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>MTECH-AI-Y1-G1</t>
+          <t>BSC-AI-Y1-G1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>M.Tech Artificial Intelligence Year 1 Group 1</t>
+          <t>B.Sc Artificial Intelligence Year 1 Group 1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -3939,14 +3939,14 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>ONLINE</t>
+          <t>CR206</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>assignment:53:session:1</t>
+          <t>assignment:23:session:3</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -3955,37 +3955,37 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Mathematics for Computing</t>
+          <t>Computer Fundamentals</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>MTECH-AI</t>
+          <t>BSC-AI</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>M.Tech Artificial Intelligence</t>
+          <t>B.Sc Artificial Intelligence</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>MTECH-AI-Y1-G1</t>
+          <t>BSC-AI-Y1-G1</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>M.Tech Artificial Intelligence Year 1 Group 1</t>
+          <t>B.Sc Artificial Intelligence Year 1 Group 1</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>ONLINE</t>
+          <t>CR202</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>assignment:12:session:1</t>
+          <t>assignment:42:session:2</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -4103,37 +4103,37 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Data Management and AI Integration</t>
+          <t>Web Technologies</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI</t>
+          <t>BCA-AI</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI-Y3-G1</t>
+          <t>BCA-AI-Y2-G1</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence Year 3 Group 1</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence Year 2 Group 1</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -4143,14 +4143,14 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>CR202</t>
+          <t>CR205</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>assignment:72:session:3</t>
+          <t>assignment:72:session:1</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1</v>
@@ -4199,14 +4199,14 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>CR204</t>
+          <t>CR206</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>assignment:72:session:2</t>
+          <t>assignment:42:session:1</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -4215,37 +4215,37 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning</t>
+          <t>Web Technologies</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>MSC-AI</t>
+          <t>BCA-AI</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>M.Sc Artificial Intelligence</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>MSC-AI-Y1-G1</t>
+          <t>BCA-AI-Y2-G1</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>M.Sc Artificial Intelligence Year 1 Group 1</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence Year 2 Group 1</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -4262,7 +4262,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>assignment:72:session:1</t>
+          <t>assignment:42:session:3</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -4271,37 +4271,37 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning</t>
+          <t>Web Technologies</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>MSC-AI</t>
+          <t>BCA-AI</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>M.Sc Artificial Intelligence</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>MSC-AI-Y1-G1</t>
+          <t>BCA-AI-Y2-G1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>M.Sc Artificial Intelligence Year 1 Group 1</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence Year 2 Group 1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -4318,46 +4318,46 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>assignment:42:session:3</t>
+          <t>assignment:12:session:1</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>WEDNESDAY</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Web Technologies</t>
+          <t>Data Management and AI Integration</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI</t>
+          <t>BTECH-AI</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
+          <t>B.Tech Artificial Intelligence</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI-Y2-G1</t>
+          <t>BTECH-AI-Y3-G1</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence Year 2 Group 1</t>
+          <t>B.Tech Artificial Intelligence Year 3 Group 1</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -4367,53 +4367,53 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>CR207</t>
+          <t>CR203</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>assignment:42:session:1</t>
+          <t>assignment:12:session:2</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>WEDNESDAY</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Web Technologies</t>
+          <t>Data Management and AI Integration</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI</t>
+          <t>BTECH-AI</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
+          <t>B.Tech Artificial Intelligence</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI-Y2-G1</t>
+          <t>BTECH-AI-Y3-G1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence Year 2 Group 1</t>
+          <t>B.Tech Artificial Intelligence Year 3 Group 1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -4423,26 +4423,26 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>CR206</t>
+          <t>CR203</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>assignment:12:session:2</t>
+          <t>assignment:12:session:3</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>WEDNESDAY</t>
+          <t>THURSDAY</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
@@ -4479,53 +4479,53 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>CR203</t>
+          <t>CR202</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>assignment:42:session:2</t>
+          <t>assignment:72:session:3</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>THURSDAY</t>
+          <t>FRIDAY</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Web Technologies</t>
+          <t>Machine Learning</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI</t>
+          <t>MSC-AI</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
+          <t>M.Sc Artificial Intelligence</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI-Y2-G1</t>
+          <t>MSC-AI-Y1-G1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence Year 2 Group 1</t>
+          <t>M.Sc Artificial Intelligence Year 1 Group 1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -4535,14 +4535,14 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>CR202</t>
+          <t>CR204</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>assignment:12:session:3</t>
+          <t>assignment:72:session:2</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -4551,37 +4551,37 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Data Management and AI Integration</t>
+          <t>Machine Learning</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI</t>
+          <t>MSC-AI</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence</t>
+          <t>M.Sc Artificial Intelligence</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI-Y3-G1</t>
+          <t>MSC-AI-Y1-G1</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence Year 3 Group 1</t>
+          <t>M.Sc Artificial Intelligence Year 1 Group 1</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>CR201</t>
+          <t>CR203</t>
         </is>
       </c>
     </row>
@@ -4690,7 +4690,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>assignment:37:session:1</t>
+          <t>assignment:67:session:2</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -4709,27 +4709,27 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Mathematics for Computing</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI</t>
+          <t>MCA-AI</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
+          <t>MCA Artificial Intelligence</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI-Y1-G1</t>
+          <t>MCA-AI-Y2-G1</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence Year 1 Group 1</t>
+          <t>MCA Artificial Intelligence Year 2 Group 1</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -4739,14 +4739,14 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>CR201</t>
+          <t>CR207</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>assignment:7:session:2</t>
+          <t>assignment:37:session:1</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Computer Organization</t>
+          <t>Mathematics for Computing</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI</t>
+          <t>BCA-AI</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI-Y2-G1</t>
+          <t>BCA-AI-Y1-G1</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence Year 2 Group 1</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence Year 1 Group 1</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -4795,14 +4795,14 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>CR204</t>
+          <t>CR206</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>assignment:67:session:3</t>
+          <t>assignment:7:session:1</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -4821,27 +4821,27 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Computer Organization</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>MCA-AI</t>
+          <t>BTECH-AI</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>MCA Artificial Intelligence</t>
+          <t>B.Tech Artificial Intelligence</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>MCA-AI-Y2-G1</t>
+          <t>BTECH-AI-Y2-G1</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>MCA Artificial Intelligence Year 2 Group 1</t>
+          <t>B.Tech Artificial Intelligence Year 2 Group 1</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -4851,14 +4851,14 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>CR201</t>
+          <t>CR204</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>assignment:67:session:1</t>
+          <t>assignment:67:session:3</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -4867,10 +4867,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>1</v>
@@ -4907,53 +4907,53 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>CR207</t>
+          <t>CR201</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>assignment:67:session:2</t>
+          <t>assignment:7:session:3</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>WEDNESDAY</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Computer Organization</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>MCA-AI</t>
+          <t>BTECH-AI</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>MCA Artificial Intelligence</t>
+          <t>B.Tech Artificial Intelligence</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>MCA-AI-Y2-G1</t>
+          <t>BTECH-AI-Y2-G1</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>MCA Artificial Intelligence Year 2 Group 1</t>
+          <t>B.Tech Artificial Intelligence Year 2 Group 1</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -4963,14 +4963,14 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>CR203</t>
+          <t>CR202</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>assignment:7:session:3</t>
+          <t>assignment:37:session:2</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -4979,37 +4979,37 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Computer Organization</t>
+          <t>Mathematics for Computing</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI</t>
+          <t>BCA-AI</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI-Y2-G1</t>
+          <t>BCA-AI-Y1-G1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence Year 2 Group 1</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence Year 1 Group 1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -5019,53 +5019,53 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>CR203</t>
+          <t>CR205</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>assignment:37:session:3</t>
+          <t>assignment:67:session:1</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>WEDNESDAY</t>
+          <t>THURSDAY</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Mathematics for Computing</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI</t>
+          <t>MCA-AI</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
+          <t>MCA Artificial Intelligence</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI-Y1-G1</t>
+          <t>MCA-AI-Y2-G1</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence Year 1 Group 1</t>
+          <t>MCA Artificial Intelligence Year 2 Group 1</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -5075,19 +5075,19 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>CR201</t>
+          <t>CR204</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>assignment:37:session:2</t>
+          <t>assignment:7:session:2</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>THURSDAY</t>
+          <t>FRIDAY</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -5101,27 +5101,27 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Mathematics for Computing</t>
+          <t>Computer Organization</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI</t>
+          <t>BTECH-AI</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
+          <t>B.Tech Artificial Intelligence</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI-Y1-G1</t>
+          <t>BTECH-AI-Y2-G1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence Year 1 Group 1</t>
+          <t>B.Tech Artificial Intelligence Year 2 Group 1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -5131,14 +5131,14 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>CR204</t>
+          <t>CR201</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>assignment:7:session:1</t>
+          <t>assignment:37:session:3</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -5147,37 +5147,37 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Computer Organization</t>
+          <t>Mathematics for Computing</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI</t>
+          <t>BCA-AI</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI-Y2-G1</t>
+          <t>BCA-AI-Y1-G1</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence Year 2 Group 1</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence Year 1 Group 1</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -5286,12 +5286,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>assignment:52:session:3</t>
+          <t>assignment:22:session:3</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>MONDAY</t>
+          <t>WEDNESDAY</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -5305,27 +5305,27 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Programming in AI</t>
+          <t>Programming in C</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>MTECH-AI</t>
+          <t>BSC-AI</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>M.Tech Artificial Intelligence</t>
+          <t>B.Sc Artificial Intelligence</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>MTECH-AI-Y1-G1</t>
+          <t>BSC-AI-Y1-G1</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>M.Tech Artificial Intelligence Year 1 Group 1</t>
+          <t>B.Sc Artificial Intelligence Year 1 Group 1</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -5335,53 +5335,53 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>CR208</t>
+          <t>CR206</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>assignment:22:session:1</t>
+          <t>assignment:52:session:2</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>WEDNESDAY</t>
+          <t>THURSDAY</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Programming in C</t>
+          <t>Programming in AI</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>BSC-AI</t>
+          <t>MTECH-AI</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>B.Sc Artificial Intelligence</t>
+          <t>M.Tech Artificial Intelligence</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>BSC-AI-Y1-G1</t>
+          <t>MTECH-AI-Y1-G1</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>B.Sc Artificial Intelligence Year 1 Group 1</t>
+          <t>M.Tech Artificial Intelligence Year 1 Group 1</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -5391,53 +5391,53 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>CR205</t>
+          <t>CR207</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>assignment:22:session:3</t>
+          <t>assignment:52:session:3</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>WEDNESDAY</t>
+          <t>THURSDAY</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Programming in C</t>
+          <t>Programming in AI</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>BSC-AI</t>
+          <t>MTECH-AI</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>B.Sc Artificial Intelligence</t>
+          <t>M.Tech Artificial Intelligence</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>BSC-AI-Y1-G1</t>
+          <t>MTECH-AI-Y1-G1</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>B.Sc Artificial Intelligence Year 1 Group 1</t>
+          <t>M.Tech Artificial Intelligence Year 1 Group 1</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -5463,10 +5463,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>1</v>
@@ -5503,14 +5503,14 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>CR206</t>
+          <t>CR205</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>assignment:52:session:2</t>
+          <t>assignment:22:session:1</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -5519,37 +5519,37 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Programming in AI</t>
+          <t>Programming in C</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>MTECH-AI</t>
+          <t>BSC-AI</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>M.Tech Artificial Intelligence</t>
+          <t>B.Sc Artificial Intelligence</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>MTECH-AI-Y1-G1</t>
+          <t>BSC-AI-Y1-G1</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>M.Tech Artificial Intelligence Year 1 Group 1</t>
+          <t>B.Sc Artificial Intelligence Year 1 Group 1</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>CR204</t>
+          <t>CR207</t>
         </is>
       </c>
     </row>
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>1</v>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>CR205</t>
+          <t>CR206</t>
         </is>
       </c>
     </row>
@@ -5714,7 +5714,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>assignment:57:session:3</t>
+          <t>assignment:57:session:1</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -5723,10 +5723,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1</v>
@@ -5763,19 +5763,19 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>CR208</t>
+          <t>CR207</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>assignment:57:session:2</t>
+          <t>assignment:27:session:3</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>MONDAY</t>
+          <t>TUESDAY</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -5789,27 +5789,27 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Natural Language Processing</t>
+          <t>Algorithms</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>MTECH-AI</t>
+          <t>BSC-AI</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>M.Tech Artificial Intelligence</t>
+          <t>B.Sc Artificial Intelligence</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>MTECH-AI-Y2-G1</t>
+          <t>BSC-AI-Y2-G1</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>M.Tech Artificial Intelligence Year 2 Group 1</t>
+          <t>B.Sc Artificial Intelligence Year 2 Group 1</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -5819,26 +5819,26 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>CR201</t>
+          <t>CR205</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>assignment:27:session:1</t>
+          <t>assignment:27:session:2</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>WEDNESDAY</t>
+          <t>TUESDAY</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1</v>
@@ -5875,14 +5875,14 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>CR203</t>
+          <t>CR204</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>assignment:27:session:3</t>
+          <t>assignment:27:session:1</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -5891,10 +5891,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>1</v>
@@ -5931,53 +5931,53 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>CR203</t>
+          <t>CR205</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>assignment:27:session:2</t>
+          <t>assignment:57:session:3</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>FRIDAY</t>
+          <t>THURSDAY</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Algorithms</t>
+          <t>Natural Language Processing</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>BSC-AI</t>
+          <t>MTECH-AI</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>B.Sc Artificial Intelligence</t>
+          <t>M.Tech Artificial Intelligence</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>BSC-AI-Y2-G1</t>
+          <t>MTECH-AI-Y2-G1</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>B.Sc Artificial Intelligence Year 2 Group 1</t>
+          <t>M.Tech Artificial Intelligence Year 2 Group 1</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -5987,14 +5987,14 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>CR201</t>
+          <t>CR203</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>assignment:57:session:1</t>
+          <t>assignment:57:session:2</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -6003,10 +6003,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>1</v>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>CR208</t>
+          <t>CR205</t>
         </is>
       </c>
     </row>
@@ -6142,7 +6142,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>assignment:69:session:1</t>
+          <t>assignment:19:session:1</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -6151,10 +6151,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>2</v>
@@ -6166,22 +6166,22 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>MCA-AI</t>
+          <t>BTECH-AI</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>MCA Artificial Intelligence</t>
+          <t>B.Tech Artificial Intelligence</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>MCA-AI-Y2-G1-B1</t>
+          <t>BTECH-AI-Y4-G1-B1</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>MCA Artificial Intelligence Year 2 Group 1 Batch 1</t>
+          <t>B.Tech Artificial Intelligence Year 4 Group 1 Batch 1</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -6191,53 +6191,53 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>LAB303</t>
+          <t>LAB301</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>assignment:44:session:1</t>
+          <t>assignment:69:session:1</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>WEDNESDAY</t>
+          <t>THURSDAY</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Web Technologies Laboratory</t>
+          <t>Artificial Intelligence Laboratory</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI</t>
+          <t>MCA-AI</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
+          <t>MCA Artificial Intelligence</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI-Y2-G1-B1</t>
+          <t>MCA-AI-Y2-G1-B1</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence Year 2 Group 1 Batch 1</t>
+          <t>MCA Artificial Intelligence Year 2 Group 1 Batch 1</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -6247,14 +6247,14 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>LAB301</t>
+          <t>LAB304</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>assignment:19:session:1</t>
+          <t>assignment:44:session:1</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -6263,37 +6263,37 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Laboratory</t>
+          <t>Web Technologies Laboratory</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI</t>
+          <t>BCA-AI</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI-Y4-G1-B1</t>
+          <t>BCA-AI-Y2-G1-B1</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence Year 4 Group 1 Batch 1</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence Year 2 Group 1 Batch 1</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -6402,7 +6402,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>assignment:38:session:3</t>
+          <t>assignment:8:session:3</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -6411,37 +6411,37 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Computer Fundamentals</t>
+          <t>Probability and Statistics</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI</t>
+          <t>BTECH-AI</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
+          <t>B.Tech Artificial Intelligence</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI-Y1-G1</t>
+          <t>BTECH-AI-Y2-G1</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence Year 1 Group 1</t>
+          <t>B.Tech Artificial Intelligence Year 2 Group 1</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -6451,14 +6451,14 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>CR204</t>
+          <t>CR201</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>assignment:68:session:2</t>
+          <t>assignment:8:session:2</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -6467,37 +6467,37 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Cloud Computing</t>
+          <t>Probability and Statistics</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>MCA-AI</t>
+          <t>BTECH-AI</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>MCA Artificial Intelligence</t>
+          <t>B.Tech Artificial Intelligence</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>MCA-AI-Y2-G1</t>
+          <t>BTECH-AI-Y2-G1</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>MCA Artificial Intelligence Year 2 Group 1</t>
+          <t>B.Tech Artificial Intelligence Year 2 Group 1</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -6507,14 +6507,14 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>ONLINE</t>
+          <t>CR202</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>assignment:68:session:3</t>
+          <t>assignment:8:session:1</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -6523,37 +6523,37 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Cloud Computing</t>
+          <t>Probability and Statistics</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>MCA-AI</t>
+          <t>BTECH-AI</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>MCA Artificial Intelligence</t>
+          <t>B.Tech Artificial Intelligence</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>MCA-AI-Y2-G1</t>
+          <t>BTECH-AI-Y2-G1</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>MCA Artificial Intelligence Year 2 Group 1</t>
+          <t>B.Tech Artificial Intelligence Year 2 Group 1</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -6563,53 +6563,53 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>ONLINE</t>
+          <t>CR203</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>assignment:68:session:1</t>
+          <t>assignment:38:session:3</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>WEDNESDAY</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Cloud Computing</t>
+          <t>Computer Fundamentals</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>MCA-AI</t>
+          <t>BCA-AI</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>MCA Artificial Intelligence</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>MCA-AI-Y2-G1</t>
+          <t>BCA-AI-Y1-G1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>MCA Artificial Intelligence Year 2 Group 1</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence Year 1 Group 1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -6619,53 +6619,53 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>ONLINE</t>
+          <t>CR206</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>assignment:8:session:1</t>
+          <t>assignment:68:session:3</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>WEDNESDAY</t>
+          <t>THURSDAY</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Probability and Statistics</t>
+          <t>Cloud Computing</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI</t>
+          <t>MCA-AI</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence</t>
+          <t>MCA Artificial Intelligence</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI-Y2-G1</t>
+          <t>MCA-AI-Y2-G1</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence Year 2 Group 1</t>
+          <t>MCA Artificial Intelligence Year 2 Group 1</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -6675,53 +6675,53 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>CR204</t>
+          <t>ONLINE</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>assignment:8:session:3</t>
+          <t>assignment:38:session:1</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>WEDNESDAY</t>
+          <t>THURSDAY</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Probability and Statistics</t>
+          <t>Computer Fundamentals</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI</t>
+          <t>BCA-AI</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI-Y2-G1</t>
+          <t>BCA-AI-Y1-G1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence Year 2 Group 1</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence Year 1 Group 1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -6731,53 +6731,53 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>CR204</t>
+          <t>CR202</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>assignment:8:session:2</t>
+          <t>assignment:68:session:2</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>WEDNESDAY</t>
+          <t>FRIDAY</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Probability and Statistics</t>
+          <t>Cloud Computing</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI</t>
+          <t>MCA-AI</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence</t>
+          <t>MCA Artificial Intelligence</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI-Y2-G1</t>
+          <t>MCA-AI-Y2-G1</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence Year 2 Group 1</t>
+          <t>MCA Artificial Intelligence Year 2 Group 1</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -6787,53 +6787,53 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>CR203</t>
+          <t>ONLINE</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>assignment:38:session:2</t>
+          <t>assignment:68:session:1</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>THURSDAY</t>
+          <t>FRIDAY</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Computer Fundamentals</t>
+          <t>Cloud Computing</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI</t>
+          <t>MCA-AI</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
+          <t>MCA Artificial Intelligence</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI-Y1-G1</t>
+          <t>MCA-AI-Y2-G1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence Year 1 Group 1</t>
+          <t>MCA Artificial Intelligence Year 2 Group 1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -6843,14 +6843,14 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>CR205</t>
+          <t>ONLINE</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>assignment:38:session:1</t>
+          <t>assignment:38:session:2</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -6859,10 +6859,10 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>1</v>
@@ -6899,7 +6899,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>CR201</t>
+          <t>CR203</t>
         </is>
       </c>
     </row>
@@ -6998,7 +6998,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>assignment:55:session:1</t>
+          <t>assignment:5:session:1</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -7007,37 +7007,37 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Advanced Machine Learning Laboratory</t>
+          <t>Programming Fundamentals Laboratory</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>MTECH-AI</t>
+          <t>BTECH-AI</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>M.Tech Artificial Intelligence</t>
+          <t>B.Tech Artificial Intelligence</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>MTECH-AI-Y1-G1-B2</t>
+          <t>BTECH-AI-Y1-G1-B2</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>M.Tech Artificial Intelligence Year 1 Group 1 Batch 2</t>
+          <t>B.Tech Artificial Intelligence Year 1 Group 1 Batch 2</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -7047,14 +7047,14 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>LAB304</t>
+          <t>LAB302</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>assignment:80:session:1</t>
+          <t>assignment:55:session:1</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -7063,37 +7063,37 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>AI Research Laboratory</t>
+          <t>Advanced Machine Learning Laboratory</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>MSC-AI</t>
+          <t>MTECH-AI</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>M.Sc Artificial Intelligence</t>
+          <t>M.Tech Artificial Intelligence</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>MSC-AI-Y2-G1-B2</t>
+          <t>MTECH-AI-Y1-G1-B2</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>M.Sc Artificial Intelligence Year 2 Group 1 Batch 2</t>
+          <t>M.Tech Artificial Intelligence Year 1 Group 1 Batch 2</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -7103,19 +7103,19 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>LAB301</t>
+          <t>LAB304</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>assignment:5:session:1</t>
+          <t>assignment:30:session:1</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>THURSDAY</t>
+          <t>WEDNESDAY</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -7129,27 +7129,27 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Programming Fundamentals Laboratory</t>
+          <t>Web Technologies Laboratory</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI</t>
+          <t>BSC-AI</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence</t>
+          <t>B.Sc Artificial Intelligence</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI-Y1-G1-B2</t>
+          <t>BSC-AI-Y2-G1-B2</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence Year 1 Group 1 Batch 2</t>
+          <t>B.Sc Artificial Intelligence Year 2 Group 1 Batch 2</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -7159,53 +7159,53 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>LAB301</t>
+          <t>LAB304</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>assignment:30:session:1</t>
+          <t>assignment:80:session:1</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>FRIDAY</t>
+          <t>THURSDAY</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Web Technologies Laboratory</t>
+          <t>AI Research Laboratory</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>BSC-AI</t>
+          <t>MSC-AI</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>B.Sc Artificial Intelligence</t>
+          <t>M.Sc Artificial Intelligence</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>BSC-AI-Y2-G1-B2</t>
+          <t>MSC-AI-Y2-G1-B2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>B.Sc Artificial Intelligence Year 2 Group 1 Batch 2</t>
+          <t>M.Sc Artificial Intelligence Year 2 Group 1 Batch 2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -7215,7 +7215,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>LAB304</t>
+          <t>LAB302</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>assignment:74:session:1</t>
+          <t>assignment:24:session:1</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -7323,37 +7323,37 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Advanced Programming Laboratory</t>
+          <t>Programming Laboratory</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>MSC-AI</t>
+          <t>BSC-AI</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>M.Sc Artificial Intelligence</t>
+          <t>B.Sc Artificial Intelligence</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>MSC-AI-Y1-G1-B1</t>
+          <t>BSC-AI-Y1-G1-B1</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>M.Sc Artificial Intelligence Year 1 Group 1 Batch 1</t>
+          <t>B.Sc Artificial Intelligence Year 1 Group 1 Batch 1</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -7363,19 +7363,19 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>LAB301</t>
+          <t>LAB303</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>assignment:49:session:1</t>
+          <t>assignment:74:session:1</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>MONDAY</t>
+          <t>TUESDAY</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -7394,22 +7394,22 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI</t>
+          <t>MSC-AI</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
+          <t>M.Sc Artificial Intelligence</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI-Y3-G1-B1</t>
+          <t>MSC-AI-Y1-G1-B1</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence Year 3 Group 1 Batch 1</t>
+          <t>M.Sc Artificial Intelligence Year 1 Group 1 Batch 1</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -7419,53 +7419,53 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>LAB301</t>
+          <t>LAB302</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>assignment:24:session:1</t>
+          <t>assignment:49:session:1</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>WEDNESDAY</t>
+          <t>THURSDAY</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Programming Laboratory</t>
+          <t>Advanced Programming Laboratory</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>BSC-AI</t>
+          <t>BCA-AI</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>B.Sc Artificial Intelligence</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>BSC-AI-Y1-G1-B1</t>
+          <t>BCA-AI-Y3-G1-B1</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>B.Sc Artificial Intelligence Year 1 Group 1 Batch 1</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence Year 3 Group 1 Batch 1</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -7574,7 +7574,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>assignment:75:session:1</t>
+          <t>assignment:50:session:1</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -7583,10 +7583,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>2</v>
@@ -7598,22 +7598,22 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>MSC-AI</t>
+          <t>BCA-AI</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>M.Sc Artificial Intelligence</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>MSC-AI-Y1-G1-B2</t>
+          <t>BCA-AI-Y3-G1-B2</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>M.Sc Artificial Intelligence Year 1 Group 1 Batch 2</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence Year 3 Group 1 Batch 2</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>LAB302</t>
+          <t>LAB301</t>
         </is>
       </c>
     </row>
@@ -7635,14 +7635,14 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>WEDNESDAY</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>2</v>
@@ -7679,26 +7679,26 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>LAB304</t>
+          <t>LAB302</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>assignment:50:session:1</t>
+          <t>assignment:75:session:1</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>FRIDAY</t>
+          <t>THURSDAY</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" s="2" t="n">
         <v>6</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>7</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>2</v>
@@ -7710,22 +7710,22 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI</t>
+          <t>MSC-AI</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
+          <t>M.Sc Artificial Intelligence</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI-Y3-G1-B2</t>
+          <t>MSC-AI-Y1-G1-B2</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence Year 3 Group 1 Batch 2</t>
+          <t>M.Sc Artificial Intelligence Year 1 Group 1 Batch 2</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>LAB302</t>
+          <t>LAB304</t>
         </is>
       </c>
     </row>
@@ -7834,46 +7834,46 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>assignment:34:session:1</t>
+          <t>assignment:9:session:1</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>MONDAY</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Data Science Laboratory</t>
+          <t>Data Structures Laboratory</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>BSC-AI</t>
+          <t>BTECH-AI</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>B.Sc Artificial Intelligence</t>
+          <t>B.Tech Artificial Intelligence</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>BSC-AI-Y3-G1-B1</t>
+          <t>BTECH-AI-Y2-G1-B1</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>B.Sc Artificial Intelligence Year 3 Group 1 Batch 1</t>
+          <t>B.Tech Artificial Intelligence Year 2 Group 1 Batch 1</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -7883,53 +7883,53 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>LAB301</t>
+          <t>LAB303</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>assignment:59:session:1</t>
+          <t>assignment:34:session:1</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>WEDNESDAY</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Research Computing Laboratory</t>
+          <t>Data Science Laboratory</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>MTECH-AI</t>
+          <t>BSC-AI</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>M.Tech Artificial Intelligence</t>
+          <t>B.Sc Artificial Intelligence</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>MTECH-AI-Y2-G1-B1</t>
+          <t>BSC-AI-Y3-G1-B1</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>M.Tech Artificial Intelligence Year 2 Group 1 Batch 1</t>
+          <t>B.Sc Artificial Intelligence Year 3 Group 1 Batch 1</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -7946,7 +7946,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>assignment:9:session:1</t>
+          <t>assignment:59:session:1</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -7955,37 +7955,37 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D4" s="2" t="n">
         <v>7</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>8</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Data Structures Laboratory</t>
+          <t>Research Computing Laboratory</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI</t>
+          <t>MTECH-AI</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence</t>
+          <t>M.Tech Artificial Intelligence</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI-Y2-G1-B1</t>
+          <t>MTECH-AI-Y2-G1-B1</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence Year 2 Group 1 Batch 1</t>
+          <t>M.Tech Artificial Intelligence Year 2 Group 1 Batch 1</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -8094,7 +8094,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>assignment:60:session:1</t>
+          <t>assignment:35:session:1</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -8103,37 +8103,37 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Research Computing Laboratory</t>
+          <t>Data Science Laboratory</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>MTECH-AI</t>
+          <t>BSC-AI</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>M.Tech Artificial Intelligence</t>
+          <t>B.Sc Artificial Intelligence</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>MTECH-AI-Y2-G1-B2</t>
+          <t>BSC-AI-Y3-G1-B2</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>M.Tech Artificial Intelligence Year 2 Group 1 Batch 2</t>
+          <t>B.Sc Artificial Intelligence Year 3 Group 1 Batch 2</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -8143,7 +8143,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>LAB302</t>
+          <t>LAB304</t>
         </is>
       </c>
     </row>
@@ -8155,14 +8155,14 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>THURSDAY</t>
+          <t>WEDNESDAY</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>2</v>
@@ -8199,14 +8199,14 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>LAB302</t>
+          <t>LAB304</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>assignment:35:session:1</t>
+          <t>assignment:60:session:1</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -8215,37 +8215,37 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Data Science Laboratory</t>
+          <t>Research Computing Laboratory</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>BSC-AI</t>
+          <t>MTECH-AI</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>B.Sc Artificial Intelligence</t>
+          <t>M.Tech Artificial Intelligence</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>BSC-AI-Y3-G1-B2</t>
+          <t>MTECH-AI-Y2-G1-B2</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>B.Sc Artificial Intelligence Year 3 Group 1 Batch 2</t>
+          <t>M.Tech Artificial Intelligence Year 2 Group 1 Batch 2</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -8255,7 +8255,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>LAB301</t>
+          <t>LAB304</t>
         </is>
       </c>
     </row>
@@ -8354,46 +8354,46 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>assignment:65:session:1</t>
+          <t>assignment:15:session:1</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>MONDAY</t>
+          <t>TUESDAY</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Programming for Artificial Intelligence Laboratory</t>
+          <t>Machine Learning Laboratory</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>MCA-AI</t>
+          <t>BTECH-AI</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>MCA Artificial Intelligence</t>
+          <t>B.Tech Artificial Intelligence</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>MCA-AI-Y1-G1-B2</t>
+          <t>BTECH-AI-Y3-G1-B2</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>MCA Artificial Intelligence Year 1 Group 1 Batch 2</t>
+          <t>B.Tech Artificial Intelligence Year 3 Group 1 Batch 2</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -8410,12 +8410,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>assignment:15:session:1</t>
+          <t>assignment:65:session:1</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>WEDNESDAY</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -8429,27 +8429,27 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning Laboratory</t>
+          <t>Programming for Artificial Intelligence Laboratory</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI</t>
+          <t>MCA-AI</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence</t>
+          <t>MCA Artificial Intelligence</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI-Y3-G1-B2</t>
+          <t>MCA-AI-Y1-G1-B2</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence Year 3 Group 1 Batch 2</t>
+          <t>MCA Artificial Intelligence Year 1 Group 1 Batch 2</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -8459,7 +8459,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>LAB304</t>
+          <t>LAB303</t>
         </is>
       </c>
     </row>
@@ -8471,14 +8471,14 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>FRIDAY</t>
+          <t>THURSDAY</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>2</v>
@@ -8515,7 +8515,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>LAB303</t>
+          <t>LAB301</t>
         </is>
       </c>
     </row>
@@ -8619,14 +8619,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>MONDAY</t>
+          <t>TUESDAY</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>2</v>
@@ -8663,7 +8663,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>LAB304</t>
+          <t>LAB303</t>
         </is>
       </c>
     </row>
@@ -8675,14 +8675,14 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>FRIDAY</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>2</v>
@@ -8719,7 +8719,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>LAB303</t>
+          <t>LAB302</t>
         </is>
       </c>
     </row>
@@ -8735,10 +8735,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>2</v>
@@ -8775,7 +8775,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>LAB303</t>
+          <t>LAB301</t>
         </is>
       </c>
     </row>
@@ -8883,10 +8883,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>2</v>
@@ -8935,14 +8935,14 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>WEDNESDAY</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>2</v>
@@ -8991,14 +8991,14 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>THURSDAY</t>
+          <t>FRIDAY</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>2</v>
@@ -9134,19 +9134,19 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>assignment:56:session:3</t>
+          <t>assignment:56:session:1</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>MONDAY</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1</v>
@@ -9183,7 +9183,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>CR203</t>
+          <t>CR208</t>
         </is>
       </c>
     </row>
@@ -9199,10 +9199,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1</v>
@@ -9239,26 +9239,26 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>CR207</t>
+          <t>CR208</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>assignment:26:session:2</t>
+          <t>assignment:26:session:1</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>FRIDAY</t>
+          <t>TUESDAY</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1</v>
@@ -9307,14 +9307,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>FRIDAY</t>
+          <t>TUESDAY</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>1</v>
@@ -9351,53 +9351,53 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>CR205</t>
+          <t>CR206</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>assignment:56:session:1</t>
+          <t>assignment:26:session:2</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>FRIDAY</t>
+          <t>WEDNESDAY</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Advanced Machine Learning</t>
+          <t>Data Structures</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>MTECH-AI</t>
+          <t>BSC-AI</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>M.Tech Artificial Intelligence</t>
+          <t>B.Sc Artificial Intelligence</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>MTECH-AI-Y2-G1</t>
+          <t>BSC-AI-Y2-G1</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>M.Tech Artificial Intelligence Year 2 Group 1</t>
+          <t>B.Sc Artificial Intelligence Year 2 Group 1</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -9407,14 +9407,14 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>CR206</t>
+          <t>CR203</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>assignment:26:session:1</t>
+          <t>assignment:56:session:3</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -9423,37 +9423,37 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Data Structures</t>
+          <t>Advanced Machine Learning</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>BSC-AI</t>
+          <t>MTECH-AI</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>B.Sc Artificial Intelligence</t>
+          <t>M.Tech Artificial Intelligence</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>BSC-AI-Y2-G1</t>
+          <t>MTECH-AI-Y2-G1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>B.Sc Artificial Intelligence Year 2 Group 1</t>
+          <t>M.Tech Artificial Intelligence Year 2 Group 1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -9463,7 +9463,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>CR203</t>
+          <t>CR208</t>
         </is>
       </c>
     </row>
@@ -9611,7 +9611,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>LH101</t>
+          <t>LH104</t>
         </is>
       </c>
     </row>
@@ -9627,10 +9627,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1</v>
@@ -9667,14 +9667,14 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>CR202</t>
+          <t>CR201</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>assignment:61:session:1</t>
+          <t>assignment:61:session:3</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -9683,10 +9683,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1</v>
@@ -9730,46 +9730,46 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>assignment:61:session:3</t>
+          <t>assignment:1:session:2</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>WEDNESDAY</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning and Pattern Recognition</t>
+          <t>Calculus and Linear Algebra</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>MCA-AI</t>
+          <t>BTECH-AI</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>MCA Artificial Intelligence</t>
+          <t>B.Tech Artificial Intelligence</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>MCA-AI-Y1-G1</t>
+          <t>BTECH-AI-Y1-G1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>MCA Artificial Intelligence Year 1 Group 1</t>
+          <t>B.Tech Artificial Intelligence Year 1 Group 1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -9779,19 +9779,19 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>LH101</t>
+          <t>CR204</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>assignment:31:session:1</t>
+          <t>assignment:1:session:3</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>THURSDAY</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -9805,27 +9805,27 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Calculus and Linear Algebra</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>BSC-AI</t>
+          <t>BTECH-AI</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>B.Sc Artificial Intelligence</t>
+          <t>B.Tech Artificial Intelligence</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>BSC-AI-Y3-G1</t>
+          <t>BTECH-AI-Y1-G1</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>B.Sc Artificial Intelligence Year 3 Group 1</t>
+          <t>B.Tech Artificial Intelligence Year 1 Group 1</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -9835,19 +9835,19 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>CR206</t>
+          <t>CR203</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>assignment:1:session:1</t>
+          <t>assignment:61:session:1</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>THURSDAY</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -9861,27 +9861,27 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Calculus and Linear Algebra</t>
+          <t>Machine Learning and Pattern Recognition</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI</t>
+          <t>MCA-AI</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence</t>
+          <t>MCA Artificial Intelligence</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI-Y1-G1</t>
+          <t>MCA-AI-Y1-G1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence Year 1 Group 1</t>
+          <t>MCA Artificial Intelligence Year 1 Group 1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -9891,53 +9891,53 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>CR203</t>
+          <t>LH102</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>assignment:1:session:3</t>
+          <t>assignment:31:session:2</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>WEDNESDAY</t>
+          <t>THURSDAY</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Calculus and Linear Algebra</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI</t>
+          <t>BSC-AI</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence</t>
+          <t>B.Sc Artificial Intelligence</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI-Y1-G1</t>
+          <t>BSC-AI-Y3-G1</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence Year 1 Group 1</t>
+          <t>B.Sc Artificial Intelligence Year 3 Group 1</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -9947,26 +9947,26 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>CR204</t>
+          <t>CR207</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>assignment:31:session:2</t>
+          <t>assignment:31:session:1</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>THURSDAY</t>
+          <t>FRIDAY</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1</v>
@@ -10003,14 +10003,14 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>CR206</t>
+          <t>CR207</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>assignment:1:session:2</t>
+          <t>assignment:1:session:1</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -10158,7 +10158,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>assignment:36:session:1</t>
+          <t>assignment:6:session:2</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -10167,37 +10167,37 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Programming in C</t>
+          <t>Data Structures</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI</t>
+          <t>BTECH-AI</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
+          <t>B.Tech Artificial Intelligence</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI-Y1-G1</t>
+          <t>BTECH-AI-Y2-G1</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence Year 1 Group 1</t>
+          <t>B.Tech Artificial Intelligence Year 2 Group 1</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -10207,26 +10207,26 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>CR206</t>
+          <t>CR203</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>assignment:6:session:1</t>
+          <t>assignment:6:session:3</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>MONDAY</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1</v>
@@ -10263,14 +10263,14 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>CR203</t>
+          <t>CR201</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>assignment:66:session:1</t>
+          <t>assignment:36:session:3</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -10279,37 +10279,37 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Advanced Data Analytics</t>
+          <t>Programming in C</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>MCA-AI</t>
+          <t>BCA-AI</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>MCA Artificial Intelligence</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>MCA-AI-Y2-G1</t>
+          <t>BCA-AI-Y1-G1</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>MCA Artificial Intelligence Year 2 Group 1</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence Year 1 Group 1</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -10319,53 +10319,53 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>CR202</t>
+          <t>CR201</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>assignment:66:session:2</t>
+          <t>assignment:36:session:2</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>WEDNESDAY</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Advanced Data Analytics</t>
+          <t>Programming in C</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>MCA-AI</t>
+          <t>BCA-AI</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>MCA Artificial Intelligence</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>MCA-AI-Y2-G1</t>
+          <t>BCA-AI-Y1-G1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>MCA Artificial Intelligence Year 2 Group 1</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence Year 1 Group 1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -10375,53 +10375,53 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>CR205</t>
+          <t>CR206</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>assignment:36:session:2</t>
+          <t>assignment:66:session:3</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>WEDNESDAY</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Programming in C</t>
+          <t>Advanced Data Analytics</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI</t>
+          <t>MCA-AI</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
+          <t>MCA Artificial Intelligence</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI-Y1-G1</t>
+          <t>MCA-AI-Y2-G1</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence Year 1 Group 1</t>
+          <t>MCA Artificial Intelligence Year 2 Group 1</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -10431,26 +10431,26 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>CR206</t>
+          <t>CR201</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>assignment:36:session:3</t>
+          <t>assignment:36:session:1</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>WEDNESDAY</t>
+          <t>THURSDAY</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>1</v>
@@ -10487,14 +10487,14 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>CR201</t>
+          <t>CR203</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>assignment:6:session:3</t>
+          <t>assignment:6:session:1</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -10503,10 +10503,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
@@ -10543,53 +10543,53 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>CR203</t>
+          <t>CR204</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>assignment:6:session:2</t>
+          <t>assignment:66:session:2</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>THURSDAY</t>
+          <t>FRIDAY</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Data Structures</t>
+          <t>Advanced Data Analytics</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI</t>
+          <t>MCA-AI</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence</t>
+          <t>MCA Artificial Intelligence</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI-Y2-G1</t>
+          <t>MCA-AI-Y2-G1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence Year 2 Group 1</t>
+          <t>MCA Artificial Intelligence Year 2 Group 1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -10606,7 +10606,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>assignment:66:session:3</t>
+          <t>assignment:66:session:1</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -10615,10 +10615,10 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>1</v>
@@ -10655,7 +10655,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>CR203</t>
+          <t>CR205</t>
         </is>
       </c>
     </row>
@@ -10754,12 +10754,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>assignment:47:session:3</t>
+          <t>assignment:17:session:1</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>MONDAY</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -10773,27 +10773,27 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Computer Vision</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI</t>
+          <t>BTECH-AI</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
+          <t>B.Tech Artificial Intelligence</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI-Y3-G1</t>
+          <t>BTECH-AI-Y4-G1</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence Year 3 Group 1</t>
+          <t>B.Tech Artificial Intelligence Year 4 Group 1</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -10803,19 +10803,19 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>CR201</t>
+          <t>LH101</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>assignment:77:session:3</t>
+          <t>assignment:17:session:3</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>MONDAY</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -10829,27 +10829,27 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Natural Language Processing</t>
+          <t>Computer Vision</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>MSC-AI</t>
+          <t>BTECH-AI</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>M.Sc Artificial Intelligence</t>
+          <t>B.Tech Artificial Intelligence</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>MSC-AI-Y2-G1</t>
+          <t>BTECH-AI-Y4-G1</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>M.Sc Artificial Intelligence Year 2 Group 1</t>
+          <t>B.Tech Artificial Intelligence Year 4 Group 1</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -10859,14 +10859,14 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>CR202</t>
+          <t>LH103</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>assignment:17:session:1</t>
+          <t>assignment:47:session:3</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -10875,37 +10875,37 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Computer Vision</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI</t>
+          <t>BCA-AI</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI-Y4-G1</t>
+          <t>BCA-AI-Y3-G1</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence Year 4 Group 1</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence Year 3 Group 1</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -10915,7 +10915,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>LH103</t>
+          <t>CR206</t>
         </is>
       </c>
     </row>
@@ -10931,10 +10931,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>1</v>
@@ -10978,19 +10978,19 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>assignment:77:session:1</t>
+          <t>assignment:77:session:3</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>WEDNESDAY</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
@@ -11027,14 +11027,14 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>CR208</t>
+          <t>CR206</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>assignment:17:session:3</t>
+          <t>assignment:47:session:1</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -11043,37 +11043,37 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Computer Vision</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI</t>
+          <t>BCA-AI</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI-Y4-G1</t>
+          <t>BCA-AI-Y3-G1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence Year 4 Group 1</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence Year 3 Group 1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -11083,53 +11083,53 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>LH103</t>
+          <t>CR206</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>assignment:47:session:1</t>
+          <t>assignment:77:session:1</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>WEDNESDAY</t>
+          <t>THURSDAY</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Natural Language Processing</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI</t>
+          <t>MSC-AI</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
+          <t>M.Sc Artificial Intelligence</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI-Y3-G1</t>
+          <t>MSC-AI-Y2-G1</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence Year 3 Group 1</t>
+          <t>M.Sc Artificial Intelligence Year 2 Group 1</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -11139,7 +11139,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>CR206</t>
+          <t>CR202</t>
         </is>
       </c>
     </row>
@@ -11151,14 +11151,14 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>WEDNESDAY</t>
+          <t>FRIDAY</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1</v>
@@ -11195,7 +11195,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>CR202</t>
+          <t>CR207</t>
         </is>
       </c>
     </row>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>THURSDAY</t>
+          <t>FRIDAY</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>LH102</t>
+          <t>LH101</t>
         </is>
       </c>
     </row>
@@ -11350,12 +11350,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>assignment:28:session:1</t>
+          <t>assignment:28:session:3</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>MONDAY</t>
+          <t>TUESDAY</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -11399,26 +11399,26 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>CR207</t>
+          <t>CR206</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>assignment:58:session:1</t>
+          <t>assignment:58:session:3</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>MONDAY</t>
+          <t>TUESDAY</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1</v>
@@ -11462,46 +11462,46 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>assignment:58:session:2</t>
+          <t>assignment:28:session:1</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>WEDNESDAY</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Computer Vision</t>
+          <t>Computer Networks</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>MTECH-AI</t>
+          <t>BSC-AI</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>M.Tech Artificial Intelligence</t>
+          <t>B.Sc Artificial Intelligence</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>MTECH-AI-Y2-G1</t>
+          <t>BSC-AI-Y2-G1</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>M.Tech Artificial Intelligence Year 2 Group 1</t>
+          <t>B.Sc Artificial Intelligence Year 2 Group 1</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -11511,53 +11511,53 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>ONLINE</t>
+          <t>CR202</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>assignment:28:session:3</t>
+          <t>assignment:58:session:2</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>THURSDAY</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Computer Networks</t>
+          <t>Computer Vision</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>BSC-AI</t>
+          <t>MTECH-AI</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>B.Sc Artificial Intelligence</t>
+          <t>M.Tech Artificial Intelligence</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>BSC-AI-Y2-G1</t>
+          <t>MTECH-AI-Y2-G1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>B.Sc Artificial Intelligence Year 2 Group 1</t>
+          <t>M.Tech Artificial Intelligence Year 2 Group 1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -11567,7 +11567,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>CR201</t>
+          <t>ONLINE</t>
         </is>
       </c>
     </row>
@@ -11579,14 +11579,14 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>THURSDAY</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
@@ -11623,14 +11623,14 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>CR207</t>
+          <t>CR202</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>assignment:58:session:3</t>
+          <t>assignment:58:session:1</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -11639,10 +11639,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>1</v>
@@ -11778,46 +11778,46 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>assignment:46:session:2</t>
+          <t>assignment:16:session:3</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>MONDAY</t>
+          <t>TUESDAY</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Software Engineering</t>
+          <t>Generative AI</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI</t>
+          <t>BTECH-AI</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
+          <t>B.Tech Artificial Intelligence</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI-Y3-G1</t>
+          <t>BTECH-AI-Y4-G1</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence Year 3 Group 1</t>
+          <t>B.Tech Artificial Intelligence Year 4 Group 1</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -11827,53 +11827,53 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>CR204</t>
+          <t>LH101</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>assignment:76:session:2</t>
+          <t>assignment:16:session:1</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>MONDAY</t>
+          <t>TUESDAY</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Deep Learning</t>
+          <t>Generative AI</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>MSC-AI</t>
+          <t>BTECH-AI</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>M.Sc Artificial Intelligence</t>
+          <t>B.Tech Artificial Intelligence</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>MSC-AI-Y2-G1</t>
+          <t>BTECH-AI-Y4-G1</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>M.Sc Artificial Intelligence Year 2 Group 1</t>
+          <t>B.Tech Artificial Intelligence Year 4 Group 1</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -11883,53 +11883,53 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>CR202</t>
+          <t>LH101</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>assignment:46:session:3</t>
+          <t>assignment:76:session:3</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>WEDNESDAY</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Software Engineering</t>
+          <t>Deep Learning</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI</t>
+          <t>MSC-AI</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
+          <t>M.Sc Artificial Intelligence</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI-Y3-G1</t>
+          <t>MSC-AI-Y2-G1</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence Year 3 Group 1</t>
+          <t>M.Sc Artificial Intelligence Year 2 Group 1</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -11939,7 +11939,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>CR201</t>
+          <t>CR207</t>
         </is>
       </c>
     </row>
@@ -11951,14 +11951,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>THURSDAY</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>1</v>
@@ -12002,46 +12002,46 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>assignment:76:session:3</t>
+          <t>assignment:46:session:1</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>THURSDAY</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Deep Learning</t>
+          <t>Software Engineering</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>MSC-AI</t>
+          <t>BCA-AI</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>M.Sc Artificial Intelligence</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>MSC-AI-Y2-G1</t>
+          <t>BCA-AI-Y3-G1</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>M.Sc Artificial Intelligence Year 2 Group 1</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence Year 3 Group 1</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -12051,26 +12051,26 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>CR208</t>
+          <t>CR201</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>assignment:76:session:1</t>
+          <t>assignment:76:session:2</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>WEDNESDAY</t>
+          <t>THURSDAY</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>1</v>
@@ -12114,7 +12114,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>assignment:16:session:3</t>
+          <t>assignment:76:session:1</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -12123,37 +12123,37 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Generative AI</t>
+          <t>Deep Learning</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI</t>
+          <t>MSC-AI</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence</t>
+          <t>M.Sc Artificial Intelligence</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI-Y4-G1</t>
+          <t>MSC-AI-Y2-G1</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence Year 4 Group 1</t>
+          <t>M.Sc Artificial Intelligence Year 2 Group 1</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -12163,19 +12163,19 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>LH102</t>
+          <t>CR204</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>assignment:46:session:1</t>
+          <t>assignment:46:session:2</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>THURSDAY</t>
+          <t>FRIDAY</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -12226,12 +12226,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>assignment:16:session:1</t>
+          <t>assignment:46:session:3</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>THURSDAY</t>
+          <t>FRIDAY</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
@@ -12245,27 +12245,27 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Generative AI</t>
+          <t>Software Engineering</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI</t>
+          <t>BCA-AI</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI-Y4-G1</t>
+          <t>BCA-AI-Y3-G1</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence Year 4 Group 1</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence Year 3 Group 1</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>LH101</t>
+          <t>CR206</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12374,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>assignment:43:session:3</t>
+          <t>assignment:73:session:1</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -12383,37 +12383,37 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Computer Networks</t>
+          <t>Research Methodology</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI</t>
+          <t>MSC-AI</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
+          <t>M.Sc Artificial Intelligence</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>BCA-AI-Y2-G1</t>
+          <t>MSC-AI-Y1-G1</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Bachelor of Computer Applications - Artificial Intelligence Year 2 Group 1</t>
+          <t>M.Sc Artificial Intelligence Year 1 Group 1</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -12423,7 +12423,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>CR206</t>
+          <t>ONLINE</t>
         </is>
       </c>
     </row>
@@ -12479,14 +12479,14 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>CR203</t>
+          <t>CR207</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>assignment:73:session:2</t>
+          <t>assignment:13:session:2</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -12495,37 +12495,37 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Research Methodology</t>
+          <t>Numerical Methods and Optimization Techniques</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>MSC-AI</t>
+          <t>BTECH-AI</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>M.Sc Artificial Intelligence</t>
+          <t>B.Tech Artificial Intelligence</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>MSC-AI-Y1-G1</t>
+          <t>BTECH-AI-Y3-G1</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>M.Sc Artificial Intelligence Year 1 Group 1</t>
+          <t>B.Tech Artificial Intelligence Year 3 Group 1</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -12542,46 +12542,46 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>assignment:73:session:1</t>
+          <t>assignment:13:session:1</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>WEDNESDAY</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Research Methodology</t>
+          <t>Numerical Methods and Optimization Techniques</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>MSC-AI</t>
+          <t>BTECH-AI</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>M.Sc Artificial Intelligence</t>
+          <t>B.Tech Artificial Intelligence</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>MSC-AI-Y1-G1</t>
+          <t>BTECH-AI-Y3-G1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>M.Sc Artificial Intelligence Year 1 Group 1</t>
+          <t>B.Tech Artificial Intelligence Year 3 Group 1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -12598,19 +12598,19 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>assignment:43:session:2</t>
+          <t>assignment:43:session:3</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>THURSDAY</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
@@ -12647,53 +12647,53 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>CR204</t>
+          <t>CR205</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>assignment:13:session:1</t>
+          <t>assignment:73:session:2</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>WEDNESDAY</t>
+          <t>THURSDAY</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Numerical Methods and Optimization Techniques</t>
+          <t>Research Methodology</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI</t>
+          <t>MSC-AI</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence</t>
+          <t>M.Sc Artificial Intelligence</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI-Y3-G1</t>
+          <t>MSC-AI-Y1-G1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence Year 3 Group 1</t>
+          <t>M.Sc Artificial Intelligence Year 1 Group 1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -12710,46 +12710,46 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>assignment:13:session:2</t>
+          <t>assignment:43:session:2</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>THURSDAY</t>
+          <t>FRIDAY</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Numerical Methods and Optimization Techniques</t>
+          <t>Computer Networks</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI</t>
+          <t>BCA-AI</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>BTECH-AI-Y3-G1</t>
+          <t>BCA-AI-Y2-G1</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>B.Tech Artificial Intelligence Year 3 Group 1</t>
+          <t>Bachelor of Computer Applications - Artificial Intelligence Year 2 Group 1</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>ONLINE</t>
+          <t>CR206</t>
         </is>
       </c>
     </row>
